--- a/00_output/16_nonresource.xlsx
+++ b/00_output/16_nonresource.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,41 +458,49 @@
   </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>utility</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>other_nonresource_benefit</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>test_utility_1</t>
         </is>
       </c>
+      <c r="B3" s="5" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>test_utility_2</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="B4" s="3" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/16_nonresource.xlsx
+++ b/00_output/16_nonresource.xlsx
@@ -459,7 +459,7 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
